--- a/healthcare_surveys/007_public_perception_of_health_ai_tools_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/007_public_perception_of_health_ai_tools_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey Title</t>
+          <t>What is the main goal of this survey?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Which of the following health AI tools do you work with or are familiar with?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Please describe your experience with health AI tools.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>healthcare_survey</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>What kind of healthcare-related survey are you most familiar with?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>What is your current form ID?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>healthcare_survey_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>How often do you participate in health surveys?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>survey_title</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Survey Title</t>
+          <t>Briefly describe how you perceive health AI tools in the following categories.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>ai_category</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How would you rate the ease of use of health AI tools for each category?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>ai_category_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>What features are missing from the current health AI tools in each category?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>What is your current form ID for participating in health surveys?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>healthcare_survey_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What kind of healthcare-related survey topic are you interested in learning more about?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>survey_title</t>
+          <t>description_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Survey Title</t>
+          <t>What are the potential risks or limitations associated with using health AI tools?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Which health AI tool would you recommend using for the following tasks?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>description_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>What are your expectations for future health AI tool development?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,246 +842,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>survey_title</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Survey Title</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Form ID</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>survey_title</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Survey Title</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Form ID</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,75 +896,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>healthcare_surveys</t>
+          <t>google_cloud_healthcare_api</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Healthcare Surveys</t>
+          <t>Google Cloud Healthcare API</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>amazon_comprehend_medical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Amazon Comprehend Medical</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>healthcare_surveys</t>
+          <t>ibm_watson_health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Healthcare Surveys</t>
+          <t>IBM Watson Health</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>healthcare_survey_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,85 +981,340 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>healthcare_survey_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>clinical_trials</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trials</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>healthcare_survey_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>healthcare_surveys</t>
+          <t>patient_outcomes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Healthcare Surveys</t>
+          <t>Patient Outcomes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>healthcare_survey_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>healthcare_survey_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>healthcare_surveys</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Healthcare Surveys</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>healthcare_survey_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ai_category_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>very_easy</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ai_category_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>somewhat_easy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Somewhat easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ai_category_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ai_category_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>somewhat_difficult</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Somewhat difficult</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ai_category_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>very_difficult</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Very difficult</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ai_category_2_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>data_quality</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ai_category_2_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>integration_with_other_tools</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Integration with other tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ai_category_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>user_interface</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>User interface</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ai_category_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>healthcare_survey_3_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ai_for_healthcare_data_analysis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AI for healthcare data analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>healthcare_survey_3_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ai_for_healthcare_data_visualization</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AI for healthcare data visualization</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>healthcare_survey_3_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ai_for_healthcare_decision_support_systems</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AI for healthcare decision support systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>assigned_tool_2_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>google_cloud_healthcare_api</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Google Cloud Healthcare API</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>assigned_tool_2_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>amazon_comprehend_medical</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Amazon Comprehend Medical</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>assigned_tool_2_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ibm_watson_health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IBM Watson Health</t>
         </is>
       </c>
     </row>
